--- a/data/dividends_info_20260415.xlsx
+++ b/data/dividends_info_20260415.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>35.29499816894531</v>
+        <v>34.40499877929688</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2549936383880804</v>
+        <v>0.2615898944724198</v>
       </c>
       <c r="J2" t="n">
         <v>334</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>55.29999923706055</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.265822802273891</v>
+        <v>1.264679348324255</v>
       </c>
       <c r="J3" t="n">
         <v>313</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.159999847412109</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6550218449725329</v>
+        <v>0.6564551175737441</v>
       </c>
       <c r="J4" t="n">
         <v>243</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>35.27000045776367</v>
+        <v>34.40499877929688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2551743658403869</v>
+        <v>0.2615898944724198</v>
       </c>
       <c r="J6" t="n">
         <v>243</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.079999923706055</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.701923212708811</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>222</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.110000133514404</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I8" t="n">
-        <v>3.273322350730658</v>
+        <v>3.267973917318617</v>
       </c>
       <c r="J8" t="n">
         <v>215</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.900000095367432</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I9" t="n">
-        <v>1.016949136104436</v>
+        <v>1.025641042361154</v>
       </c>
       <c r="J9" t="n">
         <v>187</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>35.27000045776367</v>
+        <v>34.40499877929688</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2551743658403869</v>
+        <v>0.2615898944724198</v>
       </c>
       <c r="J11" t="n">
         <v>159</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6.309999942779541</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I13" t="n">
-        <v>3.961965170634781</v>
+        <v>4.065040587370328</v>
       </c>
       <c r="J13" t="n">
         <v>103</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9.880999565124512</v>
+        <v>9.73900032043457</v>
       </c>
       <c r="I14" t="n">
-        <v>2.631312735987594</v>
+        <v>2.669678523928813</v>
       </c>
       <c r="J14" t="n">
         <v>96</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>16.28000068664551</v>
+        <v>16.36000061035156</v>
       </c>
       <c r="I15" t="n">
-        <v>3.68550353005931</v>
+        <v>3.667481525766927</v>
       </c>
       <c r="J15" t="n">
         <v>96</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>17.89999961853027</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="I17" t="n">
-        <v>2.100558703983215</v>
+        <v>2.010695105131624</v>
       </c>
       <c r="J17" t="n">
         <v>96</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.460000038146973</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="I18" t="n">
-        <v>2.197802182446978</v>
+        <v>2.209944821245335</v>
       </c>
       <c r="J18" t="n">
         <v>89</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>34.54999923706055</v>
+        <v>34.79999923706055</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4341534104553622</v>
+        <v>0.4310344922084259</v>
       </c>
       <c r="J22" t="n">
         <v>82</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.6779660907362907</v>
       </c>
       <c r="J23" t="n">
         <v>75</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>22.92000007629395</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="I24" t="n">
-        <v>1.090750432669387</v>
+        <v>1.099384355832415</v>
       </c>
       <c r="J24" t="n">
         <v>68</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>26.20000076293945</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="I25" t="n">
-        <v>0.7442747874871527</v>
+        <v>0.7456979076275785</v>
       </c>
       <c r="J25" t="n">
         <v>68</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1.879999995231628</v>
+        <v>1.870000004768372</v>
       </c>
       <c r="I26" t="n">
-        <v>1.755319153388305</v>
+        <v>1.764705877853063</v>
       </c>
       <c r="J26" t="n">
         <v>68</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>5.179999828338623</v>
+        <v>5.139999866485596</v>
       </c>
       <c r="I27" t="n">
-        <v>5.59845578398429</v>
+        <v>5.642023492858249</v>
       </c>
       <c r="J27" t="n">
         <v>68</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.182000160217285</v>
+        <v>4.124000072479248</v>
       </c>
       <c r="I28" t="n">
-        <v>3.825920465571834</v>
+        <v>3.879728350824493</v>
       </c>
       <c r="J28" t="n">
         <v>68</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2.614000082015991</v>
+        <v>2.569999933242798</v>
       </c>
       <c r="I29" t="n">
-        <v>5.302218655368509</v>
+        <v>5.392996249035542</v>
       </c>
       <c r="J29" t="n">
         <v>68</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>57.06000137329102</v>
+        <v>57.84000015258789</v>
       </c>
       <c r="I30" t="n">
-        <v>1.104100919799301</v>
+        <v>1.089211615383809</v>
       </c>
       <c r="J30" t="n">
         <v>68</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18.5</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="I31" t="n">
-        <v>4.216216216216216</v>
+        <v>4.204851924962125</v>
       </c>
       <c r="J31" t="n">
         <v>68</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>22.07999992370605</v>
+        <v>22.25</v>
       </c>
       <c r="I32" t="n">
-        <v>3.849637694461234</v>
+        <v>3.820224719101124</v>
       </c>
       <c r="J32" t="n">
         <v>68</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>35.27000045776367</v>
+        <v>34.40499877929688</v>
       </c>
       <c r="I33" t="n">
-        <v>0.2551743658403869</v>
+        <v>0.2615898944724198</v>
       </c>
       <c r="J33" t="n">
         <v>68</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>6.697999954223633</v>
+        <v>6.673999786376953</v>
       </c>
       <c r="I34" t="n">
-        <v>2.706778161228198</v>
+        <v>2.71651192393011</v>
       </c>
       <c r="J34" t="n">
         <v>68</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>8.300000190734863</v>
+        <v>8.270000457763672</v>
       </c>
       <c r="I35" t="n">
-        <v>3.132530048496061</v>
+        <v>3.143893417272044</v>
       </c>
       <c r="J35" t="n">
         <v>68</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>10.1850004196167</v>
+        <v>10.19999980926514</v>
       </c>
       <c r="I36" t="n">
-        <v>2.719685700419682</v>
+        <v>2.715686325291771</v>
       </c>
       <c r="J36" t="n">
         <v>68</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4.046000003814697</v>
+        <v>4.013999938964844</v>
       </c>
       <c r="I37" t="n">
-        <v>2.718734550081278</v>
+        <v>2.740408611674456</v>
       </c>
       <c r="J37" t="n">
         <v>61</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>28.20000076293945</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="I39" t="n">
-        <v>3.936170106274487</v>
+        <v>3.943161687538076</v>
       </c>
       <c r="J39" t="n">
         <v>50</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>0.8930000066757202</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I40" t="n">
-        <v>3.359462460888206</v>
+        <v>3.333333421636513</v>
       </c>
       <c r="J40" t="n">
         <v>47</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>0.5360000133514404</v>
+        <v>0.5370000004768372</v>
       </c>
       <c r="I41" t="n">
-        <v>4.291044669232039</v>
+        <v>4.283053999921193</v>
       </c>
       <c r="J41" t="n">
         <v>47</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>18.75</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I42" t="n">
-        <v>3.2</v>
+        <v>3.191489491218789</v>
       </c>
       <c r="J42" t="n">
         <v>47</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>2.684999942779541</v>
+        <v>2.694999933242798</v>
       </c>
       <c r="I43" t="n">
-        <v>6.70391075739324</v>
+        <v>6.679035415908614</v>
       </c>
       <c r="J43" t="n">
         <v>40</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>13.14999961853027</v>
+        <v>13.19999980926514</v>
       </c>
       <c r="I45" t="n">
-        <v>1.901140739561037</v>
+        <v>1.893939421306082</v>
       </c>
       <c r="J45" t="n">
         <v>40</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>3.349999904632568</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="I46" t="n">
-        <v>0.8955224135533352</v>
+        <v>0.8902077453638549</v>
       </c>
       <c r="J46" t="n">
         <v>40</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.819999933242798</v>
+        <v>3.779999971389771</v>
       </c>
       <c r="I47" t="n">
-        <v>3.926701639302517</v>
+        <v>3.968253998289063</v>
       </c>
       <c r="J47" t="n">
         <v>40</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>13.5</v>
+        <v>13.44999980926514</v>
       </c>
       <c r="I48" t="n">
-        <v>4.296296296296296</v>
+        <v>4.312267719144966</v>
       </c>
       <c r="J48" t="n">
         <v>40</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2.483999967575073</v>
+        <v>2.467999935150146</v>
       </c>
       <c r="I49" t="n">
-        <v>4.186795545795708</v>
+        <v>4.213938522395987</v>
       </c>
       <c r="J49" t="n">
         <v>33</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>9.381999969482422</v>
+        <v>9.394000053405762</v>
       </c>
       <c r="I50" t="n">
-        <v>3.091025377779856</v>
+        <v>3.087076840018343</v>
       </c>
       <c r="J50" t="n">
         <v>33</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2.079999923706055</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I51" t="n">
-        <v>3.701923212708811</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J51" t="n">
         <v>33</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>36.34000015258789</v>
+        <v>36.61999893188477</v>
       </c>
       <c r="I52" t="n">
-        <v>4.512933387765025</v>
+        <v>4.478427219647087</v>
       </c>
       <c r="J52" t="n">
         <v>33</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>35.84999847412109</v>
+        <v>35.97000122070312</v>
       </c>
       <c r="I53" t="n">
-        <v>5.578800795329832</v>
+        <v>5.560188857733114</v>
       </c>
       <c r="J53" t="n">
         <v>33</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>4.03000020980835</v>
+        <v>4.026000022888184</v>
       </c>
       <c r="I54" t="n">
-        <v>2.481389448978605</v>
+        <v>2.483854928750391</v>
       </c>
       <c r="J54" t="n">
         <v>33</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>34.95000076293945</v>
+        <v>36.15999984741211</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4247782453768217</v>
+        <v>0.4105641610245332</v>
       </c>
       <c r="J55" t="n">
         <v>33</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>22.79999923706055</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="I56" t="n">
-        <v>4.035087854321391</v>
+        <v>4.017467315831535</v>
       </c>
       <c r="J56" t="n">
         <v>33</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>8.439999580383301</v>
+        <v>8.354999542236328</v>
       </c>
       <c r="I57" t="n">
-        <v>3.554502546389648</v>
+        <v>3.590664469620078</v>
       </c>
       <c r="J57" t="n">
         <v>33</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>83.18000030517578</v>
+        <v>84.62000274658203</v>
       </c>
       <c r="I58" t="n">
-        <v>1.250300548430375</v>
+        <v>1.229023831533742</v>
       </c>
       <c r="J58" t="n">
         <v>33</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>48.22000122070312</v>
+        <v>48.09999847412109</v>
       </c>
       <c r="I59" t="n">
-        <v>1.451679764162795</v>
+        <v>1.455301501468064</v>
       </c>
       <c r="J59" t="n">
         <v>33</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>55.29999923706055</v>
+        <v>55.34999847412109</v>
       </c>
       <c r="I60" t="n">
-        <v>3.978300235717942</v>
+        <v>3.974706523304803</v>
       </c>
       <c r="J60" t="n">
         <v>33</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>8.406000137329102</v>
+        <v>8.607000350952148</v>
       </c>
       <c r="I61" t="n">
-        <v>10.23078736557401</v>
+        <v>9.991866677510505</v>
       </c>
       <c r="J61" t="n">
         <v>33</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>12.35200023651123</v>
+        <v>12.40999984741211</v>
       </c>
       <c r="I62" t="n">
-        <v>4.533678669667591</v>
+        <v>4.512489982961429</v>
       </c>
       <c r="J62" t="n">
         <v>33</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>1.929999947547913</v>
+        <v>1.919999957084656</v>
       </c>
       <c r="I63" t="n">
-        <v>2.07253891642953</v>
+        <v>2.083333379899463</v>
       </c>
       <c r="J63" t="n">
         <v>33</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>9.149999618530273</v>
+        <v>9.069999694824219</v>
       </c>
       <c r="I64" t="n">
-        <v>3.278688661280925</v>
+        <v>3.307607608533818</v>
       </c>
       <c r="J64" t="n">
         <v>33</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2.25</v>
+        <v>2.279999971389771</v>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>4.736842164702693</v>
       </c>
       <c r="J65" t="n">
         <v>33</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>74.59999847412109</v>
+        <v>73.09999847412109</v>
       </c>
       <c r="I66" t="n">
-        <v>2.761394158358621</v>
+        <v>2.818057514364084</v>
       </c>
       <c r="J66" t="n">
         <v>33</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>16.31999969482422</v>
+        <v>16.10000038146973</v>
       </c>
       <c r="I68" t="n">
-        <v>1.838235328491722</v>
+        <v>1.863353993117196</v>
       </c>
       <c r="J68" t="n">
         <v>33</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>46.09999847412109</v>
+        <v>46.40000152587891</v>
       </c>
       <c r="I69" t="n">
-        <v>1.843817848447782</v>
+        <v>1.831896491481633</v>
       </c>
       <c r="J69" t="n">
         <v>33</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>33.79999923706055</v>
+        <v>33.63999938964844</v>
       </c>
       <c r="I70" t="n">
-        <v>2.514792956172626</v>
+        <v>2.526753910291563</v>
       </c>
       <c r="J70" t="n">
         <v>33</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>63.22000122070312</v>
+        <v>63.29999923706055</v>
       </c>
       <c r="I71" t="n">
-        <v>2.056311254189409</v>
+        <v>2.05371250500566</v>
       </c>
       <c r="J71" t="n">
         <v>33</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>7.880000114440918</v>
+        <v>7.820000171661377</v>
       </c>
       <c r="I72" t="n">
-        <v>7.614213087388637</v>
+        <v>7.672634102673282</v>
       </c>
       <c r="J72" t="n">
         <v>33</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>6.110000133514404</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I74" t="n">
-        <v>3.273322350730658</v>
+        <v>3.267973917318617</v>
       </c>
       <c r="J74" t="n">
         <v>33</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>22.15999984741211</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="I75" t="n">
-        <v>4.512635410134184</v>
+        <v>4.566210125199586</v>
       </c>
       <c r="J75" t="n">
         <v>33</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>4.619999885559082</v>
+        <v>4.550000190734863</v>
       </c>
       <c r="I76" t="n">
-        <v>4.653679768954845</v>
+        <v>4.725274527192398</v>
       </c>
       <c r="J76" t="n">
         <v>33</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>23.44000053405762</v>
+        <v>23.30999946594238</v>
       </c>
       <c r="I77" t="n">
-        <v>1.151877106861402</v>
+        <v>1.158301184839106</v>
       </c>
       <c r="J77" t="n">
         <v>33</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>7.920000076293945</v>
+        <v>8</v>
       </c>
       <c r="I78" t="n">
-        <v>2.525252500926582</v>
+        <v>2.5</v>
       </c>
       <c r="J78" t="n">
         <v>33</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>9.645000457763672</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I79" t="n">
-        <v>2.488335807250416</v>
+        <v>2.49999990065893</v>
       </c>
       <c r="J79" t="n">
         <v>33</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>21.38999938964844</v>
+        <v>21.64999961853027</v>
       </c>
       <c r="I80" t="n">
-        <v>3.693314738392727</v>
+        <v>3.648960803324161</v>
       </c>
       <c r="J80" t="n">
         <v>33</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5.900000095367432</v>
+        <v>5.849999904632568</v>
       </c>
       <c r="I82" t="n">
-        <v>1.016949136104436</v>
+        <v>1.025641042361154</v>
       </c>
       <c r="J82" t="n">
         <v>33</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>37.81999969482422</v>
+        <v>37.09999847412109</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9254362845695595</v>
+        <v>0.9433962652158614</v>
       </c>
       <c r="J83" t="n">
         <v>33</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>7.514999866485596</v>
+        <v>7.230000019073486</v>
       </c>
       <c r="I84" t="n">
-        <v>7.375914968036048</v>
+        <v>7.666666646441208</v>
       </c>
       <c r="J84" t="n">
         <v>33</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>12.55000019073486</v>
+        <v>12.5</v>
       </c>
       <c r="I86" t="n">
-        <v>1.593625473788053</v>
+        <v>1.6</v>
       </c>
       <c r="J86" t="n">
         <v>33</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.920000076293945</v>
+        <v>5.929999828338623</v>
       </c>
       <c r="I87" t="n">
-        <v>1.739864842442373</v>
+        <v>1.736930910314326</v>
       </c>
       <c r="J87" t="n">
         <v>33</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>5.76200008392334</v>
+        <v>5.791999816894531</v>
       </c>
       <c r="I88" t="n">
-        <v>3.297466109556687</v>
+        <v>3.280386844036045</v>
       </c>
       <c r="J88" t="n">
         <v>33</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>26.95999908447266</v>
+        <v>27</v>
       </c>
       <c r="I90" t="n">
-        <v>1.632047533167067</v>
+        <v>1.62962962962963</v>
       </c>
       <c r="J90" t="n">
         <v>33</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1.080000042915344</v>
+        <v>1.120000004768372</v>
       </c>
       <c r="I91" t="n">
-        <v>2.77777766739881</v>
+        <v>2.678571417167479</v>
       </c>
       <c r="J91" t="n">
         <v>33</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>8.399999618530273</v>
+        <v>8.289999961853027</v>
       </c>
       <c r="I92" t="n">
-        <v>5.595238349335005</v>
+        <v>5.669481328862912</v>
       </c>
       <c r="J92" t="n">
         <v>33</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>53.65999984741211</v>
+        <v>54.36000061035156</v>
       </c>
       <c r="I93" t="n">
-        <v>2.609019761425733</v>
+        <v>2.575423076307699</v>
       </c>
       <c r="J93" t="n">
         <v>33</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>3.50600004196167</v>
+        <v>3.665999889373779</v>
       </c>
       <c r="I94" t="n">
-        <v>8.556759737861972</v>
+        <v>8.183306302588175</v>
       </c>
       <c r="J94" t="n">
         <v>33</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>3.440000057220459</v>
+        <v>3.450000047683716</v>
       </c>
       <c r="I96" t="n">
-        <v>4.941860382914093</v>
+        <v>4.927536163778773</v>
       </c>
       <c r="J96" t="n">
         <v>33</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>20.79999923706055</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="I97" t="n">
-        <v>3.365384738826191</v>
+        <v>3.357314087255938</v>
       </c>
       <c r="J97" t="n">
         <v>33</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>2.759999990463257</v>
+        <v>2.680000066757202</v>
       </c>
       <c r="I98" t="n">
-        <v>1.268115946410759</v>
+        <v>1.305970116722794</v>
       </c>
       <c r="J98" t="n">
         <v>33</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>0.9739999771118164</v>
+        <v>0.9760000109672546</v>
       </c>
       <c r="I100" t="n">
-        <v>7.186858485106917</v>
+        <v>7.172131066948169</v>
       </c>
       <c r="J100" t="n">
         <v>33</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>49.65999984741211</v>
+        <v>50</v>
       </c>
       <c r="I101" t="n">
-        <v>1.429722114743421</v>
+        <v>1.42</v>
       </c>
       <c r="J101" t="n">
         <v>33</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>86.84999847412109</v>
+        <v>87.65000152587891</v>
       </c>
       <c r="I102" t="n">
-        <v>1.554404172387249</v>
+        <v>1.540216744436004</v>
       </c>
       <c r="J102" t="n">
         <v>33</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>7.199999809265137</v>
+        <v>7.179999828338623</v>
       </c>
       <c r="I103" t="n">
-        <v>1.111111140545505</v>
+        <v>1.114206154772446</v>
       </c>
       <c r="J103" t="n">
         <v>33</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I104" t="n">
-        <v>1.181102362204724</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="J104" t="n">
         <v>33</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>4.11299991607666</v>
+        <v>4.139999866485596</v>
       </c>
       <c r="I105" t="n">
-        <v>4.133236165055917</v>
+        <v>4.106280325663665</v>
       </c>
       <c r="J105" t="n">
         <v>33</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>57.90000152587891</v>
+        <v>57.09999847412109</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7772020520567148</v>
+        <v>0.7880910893613235</v>
       </c>
       <c r="J107" t="n">
         <v>33</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>4.800000190734863</v>
+        <v>4.739999771118164</v>
       </c>
       <c r="I108" t="n">
-        <v>0.833333300219643</v>
+        <v>0.8438818972888689</v>
       </c>
       <c r="J108" t="n">
         <v>33</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>32.90000152587891</v>
+        <v>33.27999877929688</v>
       </c>
       <c r="I109" t="n">
-        <v>3.191489213683099</v>
+        <v>3.155048192649555</v>
       </c>
       <c r="J109" t="n">
         <v>33</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>1.549999952316284</v>
+        <v>1.620000004768372</v>
       </c>
       <c r="I110" t="n">
-        <v>3.225806550850609</v>
+        <v>3.086419744001731</v>
       </c>
       <c r="J110" t="n">
         <v>33</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>19.29999923706055</v>
+        <v>19.14999961853027</v>
       </c>
       <c r="I111" t="n">
-        <v>1.968911994930603</v>
+        <v>1.98433424318347</v>
       </c>
       <c r="J111" t="n">
         <v>33</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>24.93000030517578</v>
+        <v>24.8700008392334</v>
       </c>
       <c r="I112" t="n">
-        <v>2.406738839371103</v>
+        <v>2.412545153812285</v>
       </c>
       <c r="J112" t="n">
         <v>33</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>32.29999923706055</v>
+        <v>32.20000076293945</v>
       </c>
       <c r="I113" t="n">
-        <v>1.083591356864229</v>
+        <v>1.086956495985031</v>
       </c>
       <c r="J113" t="n">
         <v>33</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>3.079999923706055</v>
+        <v>3.279999971389771</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5519480656202258</v>
+        <v>0.5182926874477052</v>
       </c>
       <c r="J114" t="n">
         <v>33</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>22.04000091552734</v>
+        <v>22.10000038146973</v>
       </c>
       <c r="I116" t="n">
-        <v>5.081669480380792</v>
+        <v>5.067873215690489</v>
       </c>
       <c r="J116" t="n">
         <v>33</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1.409999966621399</v>
+        <v>1.480000019073486</v>
       </c>
       <c r="I117" t="n">
-        <v>7.092198749452251</v>
+        <v>6.756756669679118</v>
       </c>
       <c r="J117" t="n">
         <v>33</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>2.584000110626221</v>
+        <v>2.589999914169312</v>
       </c>
       <c r="I118" t="n">
-        <v>10.06191907387303</v>
+        <v>10.03861037128218</v>
       </c>
       <c r="J118" t="n">
         <v>33</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>2.157999992370605</v>
+        <v>2.196000099182129</v>
       </c>
       <c r="I119" t="n">
-        <v>4.277108448856231</v>
+        <v>4.20309634932967</v>
       </c>
       <c r="J119" t="n">
         <v>33</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>9.199999809265137</v>
+        <v>9.119999885559082</v>
       </c>
       <c r="I120" t="n">
-        <v>3.804347904958889</v>
+        <v>3.837719346402645</v>
       </c>
       <c r="J120" t="n">
         <v>26</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>4.820000171661377</v>
+        <v>4.860000133514404</v>
       </c>
       <c r="I121" t="n">
-        <v>1.991701173880049</v>
+        <v>1.975308587709434</v>
       </c>
       <c r="J121" t="n">
         <v>26</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>5.949999809265137</v>
+        <v>6</v>
       </c>
       <c r="I122" t="n">
-        <v>5.042016968350994</v>
+        <v>5</v>
       </c>
       <c r="J122" t="n">
         <v>26</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>12</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I123" t="n">
-        <v>1.666666666666667</v>
+        <v>1.694915226840727</v>
       </c>
       <c r="J123" t="n">
         <v>26</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>9.159999847412109</v>
+        <v>9.140000343322754</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6550218449725329</v>
+        <v>0.6564551175737441</v>
       </c>
       <c r="J124" t="n">
         <v>26</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.240000009536743</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I125" t="n">
-        <v>2.678571417167479</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J125" t="n">
         <v>26</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>16.23999977111816</v>
+        <v>16.13999938964844</v>
       </c>
       <c r="I126" t="n">
-        <v>3.07881777738211</v>
+        <v>3.097893549616119</v>
       </c>
       <c r="J126" t="n">
         <v>26</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>3.960000038146973</v>
+        <v>3.980000019073486</v>
       </c>
       <c r="I127" t="n">
-        <v>2.525252500926582</v>
+        <v>2.512562802029314</v>
       </c>
       <c r="J127" t="n">
         <v>26</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.740000009536743</v>
+        <v>2.710000038146973</v>
       </c>
       <c r="I128" t="n">
-        <v>4.014598526172922</v>
+        <v>4.059040533269333</v>
       </c>
       <c r="J128" t="n">
         <v>26</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.149999618530273</v>
+        <v>9.050000190734863</v>
       </c>
       <c r="I129" t="n">
-        <v>0.9289617873629289</v>
+        <v>0.9392264995421837</v>
       </c>
       <c r="J129" t="n">
         <v>26</v>
@@ -6586,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1.230000019073486</v>
+        <v>1.309999942779541</v>
       </c>
       <c r="I131" t="n">
-        <v>2.439024352422197</v>
+        <v>2.290076435907805</v>
       </c>
       <c r="J131" t="n">
         <v>26</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>7.199999809265137</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I134" t="n">
-        <v>3.055555636500137</v>
+        <v>3.072625763805235</v>
       </c>
       <c r="J134" t="n">
         <v>26</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>3.460000038146973</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I135" t="n">
-        <v>4.624277405664109</v>
+        <v>4.692081993335886</v>
       </c>
       <c r="J135" t="n">
         <v>19</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>23.95000076293945</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="I136" t="n">
-        <v>2.546972778990146</v>
+        <v>2.6068376493346</v>
       </c>
       <c r="J136" t="n">
         <v>19</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>3.029999971389771</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="I137" t="n">
-        <v>4.950495096249109</v>
+        <v>4.934210588231972</v>
       </c>
       <c r="J137" t="n">
         <v>19</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>12.69999980926514</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="I138" t="n">
-        <v>5.511811106401145</v>
+        <v>5.555555387359032</v>
       </c>
       <c r="J138" t="n">
         <v>19</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.390000343322754</v>
+        <v>9.319999694824219</v>
       </c>
       <c r="I139" t="n">
-        <v>5.436634519007419</v>
+        <v>5.477467990514009</v>
       </c>
       <c r="J139" t="n">
         <v>19</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>7.625</v>
+        <v>7.730000019073486</v>
       </c>
       <c r="I140" t="n">
-        <v>3.540983606557377</v>
+        <v>3.492884855547026</v>
       </c>
       <c r="J140" t="n">
         <v>19</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>5.690000057220459</v>
+        <v>5.675000190734863</v>
       </c>
       <c r="I141" t="n">
-        <v>6.151142293150934</v>
+        <v>6.167400673772982</v>
       </c>
       <c r="J141" t="n">
         <v>19</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>18.60000038146973</v>
+        <v>18.64999961853027</v>
       </c>
       <c r="I143" t="n">
-        <v>4.032257981818046</v>
+        <v>4.021447803434884</v>
       </c>
       <c r="J143" t="n">
         <v>19</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>10.44999980926514</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I144" t="n">
-        <v>4.114832610989668</v>
+        <v>4.075829310198792</v>
       </c>
       <c r="J144" t="n">
         <v>19</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>4.389999866485596</v>
+        <v>4.315000057220459</v>
       </c>
       <c r="I145" t="n">
-        <v>3.416856595945233</v>
+        <v>3.476245608595047</v>
       </c>
       <c r="J145" t="n">
         <v>19</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>12.10000038146973</v>
+        <v>12.07999992370605</v>
       </c>
       <c r="I146" t="n">
-        <v>1.629495816396419</v>
+        <v>1.632193718917756</v>
       </c>
       <c r="J146" t="n">
         <v>19</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>29</v>
+        <v>29.20000076293945</v>
       </c>
       <c r="I147" t="n">
-        <v>3.793103448275863</v>
+        <v>3.767123189243599</v>
       </c>
       <c r="J147" t="n">
         <v>19</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>46.45000076293945</v>
+        <v>45.75</v>
       </c>
       <c r="I148" t="n">
-        <v>1.011840672293365</v>
+        <v>1.027322404371585</v>
       </c>
       <c r="J148" t="n">
         <v>19</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>81.69999694824219</v>
+        <v>80.30000305175781</v>
       </c>
       <c r="I149" t="n">
-        <v>1.46878830455797</v>
+        <v>1.494395958150255</v>
       </c>
       <c r="J149" t="n">
         <v>19</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>23.14999961853027</v>
+        <v>23.39999961853027</v>
       </c>
       <c r="I150" t="n">
-        <v>1.166306714682968</v>
+        <v>1.153846172656299</v>
       </c>
       <c r="J150" t="n">
         <v>19</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>10.44999980926514</v>
+        <v>10.35000038146973</v>
       </c>
       <c r="I151" t="n">
-        <v>3.636363702735056</v>
+        <v>3.671497449220761</v>
       </c>
       <c r="J151" t="n">
         <v>19</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>27.70000076293945</v>
+        <v>28.14999961853027</v>
       </c>
       <c r="I152" t="n">
-        <v>1.083032461144831</v>
+        <v>1.06571937501029</v>
       </c>
       <c r="J152" t="n">
         <v>19</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>0.1982000023126602</v>
+        <v>0.2000000029802322</v>
       </c>
       <c r="I153" t="n">
-        <v>3.531786033462053</v>
+        <v>3.499999947845937</v>
       </c>
       <c r="J153" t="n">
         <v>12</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>7.559999942779541</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I154" t="n">
-        <v>2.116402132420834</v>
+        <v>2.105263184312308</v>
       </c>
       <c r="J154" t="n">
         <v>12</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>2.200000047683716</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I155" t="n">
-        <v>2.954545390507408</v>
+        <v>2.941176419820373</v>
       </c>
       <c r="J155" t="n">
         <v>12</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>8.149999618530273</v>
+        <v>8</v>
       </c>
       <c r="I156" t="n">
-        <v>3.067484806153692</v>
+        <v>3.125</v>
       </c>
       <c r="J156" t="n">
         <v>12</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>6.820000171661377</v>
+        <v>6.789999961853027</v>
       </c>
       <c r="I158" t="n">
-        <v>7.331378114587323</v>
+        <v>7.363770291738667</v>
       </c>
       <c r="J158" t="n">
         <v>5</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>18.90500068664551</v>
+        <v>19.02000045776367</v>
       </c>
       <c r="I159" t="n">
-        <v>3.438243725953208</v>
+        <v>3.417455227950218</v>
       </c>
       <c r="J159" t="n">
         <v>5</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>12.66499996185303</v>
+        <v>12.98999977111816</v>
       </c>
       <c r="I160" t="n">
-        <v>4.263718923225265</v>
+        <v>4.157043953154107</v>
       </c>
       <c r="J160" t="n">
         <v>5</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>6.607999801635742</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="I161" t="n">
-        <v>1.513317236711267</v>
+        <v>1.515151537044865</v>
       </c>
       <c r="J161" t="n">
         <v>5</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>8.979999542236328</v>
+        <v>8.899999618530273</v>
       </c>
       <c r="I162" t="n">
-        <v>1.781737284589599</v>
+        <v>1.797752886043629</v>
       </c>
       <c r="J162" t="n">
         <v>5</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>302.6000061035156</v>
+        <v>302.75</v>
       </c>
       <c r="I163" t="n">
-        <v>1.194646373788689</v>
+        <v>1.194054500412882</v>
       </c>
       <c r="J163" t="n">
         <v>5</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>29.10000038146973</v>
+        <v>28.89999961853027</v>
       </c>
       <c r="I164" t="n">
-        <v>4.673539457635265</v>
+        <v>4.705882415057152</v>
       </c>
       <c r="J164" t="n">
         <v>5</v>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>15.34000015258789</v>
+        <v>15.44999980926514</v>
       </c>
       <c r="I165" t="n">
-        <v>3.813559284100197</v>
+        <v>3.786407813734626</v>
       </c>
       <c r="J165" t="n">
         <v>5</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>18.53000068664551</v>
+        <v>19.19499969482422</v>
       </c>
       <c r="I166" t="n">
-        <v>3.399891940932513</v>
+        <v>3.28210476695071</v>
       </c>
       <c r="J166" t="n">
         <v>5</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>121.5999984741211</v>
+        <v>121.4499969482422</v>
       </c>
       <c r="I167" t="n">
-        <v>0.7401315882347959</v>
+        <v>0.7410457164387982</v>
       </c>
       <c r="J167" t="n">
         <v>5</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>69.97000122070312</v>
+        <v>70.19999694824219</v>
       </c>
       <c r="I168" t="n">
-        <v>2.459339674115712</v>
+        <v>2.451282157845007</v>
       </c>
       <c r="J168" t="n">
         <v>5</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>27.20000076293945</v>
+        <v>27</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5147058679158305</v>
+        <v>0.5185185185185186</v>
       </c>
       <c r="J169" t="n">
         <v>-2</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>1.639999985694885</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="I170" t="n">
-        <v>3.658536617277918</v>
+        <v>3.773584826442149</v>
       </c>
       <c r="J170" t="n">
         <v>-2</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>2</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>1.65048548273861</v>
       </c>
       <c r="J171" t="n">
         <v>-16</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>23.41500091552734</v>
+        <v>23.30999946594238</v>
       </c>
       <c r="I172" t="n">
-        <v>1.110399273260692</v>
+        <v>1.115401140956177</v>
       </c>
       <c r="J172" t="n">
         <v>-23</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>35.27000045776367</v>
+        <v>34.40499877929688</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2551743658403869</v>
+        <v>0.2615898944724198</v>
       </c>
       <c r="J173" t="n">
         <v>-23</v>
@@ -10085,7 +10085,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10102,7 +10102,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10119,7 +10119,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10136,7 +10136,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10153,7 +10153,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10170,7 +10170,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10187,7 +10187,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10197,14 +10197,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10221,7 +10221,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10248,14 +10248,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10265,14 +10265,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10289,7 +10289,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10306,7 +10306,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10323,7 +10323,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10340,7 +10340,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10350,14 +10350,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10374,7 +10374,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10391,7 +10391,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10425,7 +10425,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10442,7 +10442,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10459,7 +10459,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10476,7 +10476,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10493,7 +10493,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10510,7 +10510,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10527,7 +10527,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10544,7 +10544,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10561,7 +10561,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10578,7 +10578,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10595,7 +10595,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10612,7 +10612,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10622,14 +10622,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10639,14 +10639,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10663,7 +10663,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10680,7 +10680,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10697,7 +10697,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10707,14 +10707,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10731,7 +10731,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -10741,14 +10741,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -10765,7 +10765,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -10782,7 +10782,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -10792,14 +10792,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -10809,14 +10809,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -10833,7 +10833,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -10843,14 +10843,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -10867,7 +10867,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -10877,14 +10877,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10894,14 +10894,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10911,14 +10911,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10935,7 +10935,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10945,14 +10945,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10969,7 +10969,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10979,14 +10979,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11020,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11037,7 +11037,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11047,14 +11047,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11088,7 +11088,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11105,7 +11105,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11122,7 +11122,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11139,7 +11139,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11156,7 +11156,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11166,14 +11166,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11183,14 +11183,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11207,7 +11207,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11224,7 +11224,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11241,7 +11241,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11258,7 +11258,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11275,7 +11275,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11292,7 +11292,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11309,7 +11309,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11326,7 +11326,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11336,14 +11336,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11360,7 +11360,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11370,14 +11370,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11394,7 +11394,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11404,14 +11404,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11428,7 +11428,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11445,7 +11445,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11462,7 +11462,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11479,7 +11479,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11496,7 +11496,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11513,7 +11513,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11530,7 +11530,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11547,7 +11547,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11564,7 +11564,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11581,7 +11581,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11591,14 +11591,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11632,7 +11632,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11649,7 +11649,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11683,7 +11683,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11717,7 +11717,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11727,14 +11727,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11751,7 +11751,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11768,7 +11768,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11778,14 +11778,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11802,7 +11802,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11819,7 +11819,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11836,7 +11836,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11853,7 +11853,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11870,7 +11870,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11887,7 +11887,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11904,7 +11904,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11921,7 +11921,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11938,7 +11938,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11955,7 +11955,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11972,7 +11972,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11982,14 +11982,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12006,7 +12006,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12016,14 +12016,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12040,7 +12040,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12057,7 +12057,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12074,7 +12074,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12091,7 +12091,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12108,7 +12108,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12118,14 +12118,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12142,7 +12142,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12159,7 +12159,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12176,7 +12176,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12193,7 +12193,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12210,7 +12210,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12227,7 +12227,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12244,7 +12244,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12254,14 +12254,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12271,14 +12271,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12295,7 +12295,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12312,7 +12312,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12329,7 +12329,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12339,14 +12339,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12363,7 +12363,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12397,7 +12397,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12407,14 +12407,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12431,7 +12431,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12448,7 +12448,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12465,7 +12465,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12482,7 +12482,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12499,7 +12499,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12516,7 +12516,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12526,14 +12526,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12550,7 +12550,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12567,7 +12567,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12584,7 +12584,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12594,14 +12594,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12611,14 +12611,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12635,7 +12635,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12645,14 +12645,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12669,7 +12669,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -12686,7 +12686,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -12703,7 +12703,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -12720,7 +12720,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -12737,7 +12737,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -12754,7 +12754,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -12771,7 +12771,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -12788,7 +12788,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -12805,7 +12805,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -12822,7 +12822,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -12839,7 +12839,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -12856,7 +12856,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -12873,7 +12873,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -12890,7 +12890,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -12907,7 +12907,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -12917,14 +12917,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -12941,7 +12941,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -12958,7 +12958,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -12992,7 +12992,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13009,7 +13009,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13026,7 +13026,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13043,7 +13043,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13053,14 +13053,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13077,7 +13077,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13087,14 +13087,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13111,7 +13111,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13128,7 +13128,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13138,14 +13138,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13155,14 +13155,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13179,7 +13179,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13332,7 +13332,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13342,14 +13342,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13366,7 +13366,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13376,14 +13376,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13393,14 +13393,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13417,7 +13417,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13434,7 +13434,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13444,14 +13444,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13461,14 +13461,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13485,7 +13485,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13502,7 +13502,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13519,7 +13519,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13529,14 +13529,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13553,7 +13553,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13570,7 +13570,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13587,7 +13587,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13604,7 +13604,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13621,7 +13621,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13638,7 +13638,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13648,14 +13648,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13672,7 +13672,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -13689,7 +13689,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -13706,7 +13706,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -13716,14 +13716,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -13740,7 +13740,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -13757,7 +13757,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -13774,7 +13774,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -13784,14 +13784,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -13825,7 +13825,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -13842,7 +13842,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -13852,14 +13852,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -13869,14 +13869,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -13893,7 +13893,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -13903,14 +13903,14 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -13927,7 +13927,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -13944,7 +13944,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -13954,14 +13954,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -13978,7 +13978,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -13995,7 +13995,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14012,7 +14012,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14029,7 +14029,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14046,7 +14046,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14063,7 +14063,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14080,7 +14080,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14097,7 +14097,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14114,7 +14114,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14131,7 +14131,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14148,7 +14148,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14165,7 +14165,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14182,7 +14182,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14199,7 +14199,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14216,7 +14216,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14226,14 +14226,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14250,7 +14250,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14267,7 +14267,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14277,14 +14277,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14301,7 +14301,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14318,7 +14318,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14335,7 +14335,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14352,7 +14352,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14362,14 +14362,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14386,7 +14386,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14396,14 +14396,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14413,14 +14413,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14437,7 +14437,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14454,7 +14454,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14464,14 +14464,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14488,7 +14488,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14505,7 +14505,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14539,7 +14539,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14549,14 +14549,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14573,7 +14573,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14583,14 +14583,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14607,7 +14607,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14624,7 +14624,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14641,7 +14641,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14658,7 +14658,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14675,7 +14675,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14685,14 +14685,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14709,7 +14709,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14726,7 +14726,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14743,7 +14743,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14760,7 +14760,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14777,7 +14777,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14794,7 +14794,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14811,7 +14811,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14828,7 +14828,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14838,14 +14838,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14855,14 +14855,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14879,7 +14879,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14896,7 +14896,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14930,7 +14930,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14947,7 +14947,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14964,7 +14964,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14981,7 +14981,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -14998,7 +14998,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15015,7 +15015,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15032,7 +15032,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15049,7 +15049,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15066,7 +15066,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15083,7 +15083,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15093,14 +15093,14 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15117,7 +15117,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15134,7 +15134,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15151,7 +15151,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15168,7 +15168,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15185,7 +15185,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15202,7 +15202,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15219,7 +15219,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15253,7 +15253,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15270,7 +15270,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15287,7 +15287,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15297,14 +15297,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15321,7 +15321,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15338,7 +15338,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15355,7 +15355,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15372,7 +15372,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15389,7 +15389,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15399,14 +15399,14 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15416,14 +15416,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15433,7 +15433,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -15457,7 +15457,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15474,7 +15474,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15484,14 +15484,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15508,7 +15508,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15525,7 +15525,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15542,7 +15542,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15559,7 +15559,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15569,14 +15569,14 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15593,7 +15593,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15610,7 +15610,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15627,7 +15627,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15644,7 +15644,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15661,7 +15661,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -15671,14 +15671,14 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -15712,7 +15712,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -15729,7 +15729,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -15746,7 +15746,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -15763,7 +15763,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -15780,7 +15780,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -15790,14 +15790,14 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -15807,14 +15807,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -15824,14 +15824,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -15848,7 +15848,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -15858,14 +15858,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -15882,7 +15882,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -15892,14 +15892,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -15909,14 +15909,14 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -15926,14 +15926,14 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -15943,14 +15943,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -15967,7 +15967,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -15984,7 +15984,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -15994,7 +15994,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16018,7 +16018,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16028,14 +16028,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16045,14 +16045,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16069,7 +16069,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16079,14 +16079,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16103,7 +16103,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16120,7 +16120,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16130,14 +16130,14 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16147,14 +16147,14 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16164,14 +16164,14 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16181,14 +16181,14 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16198,7 +16198,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -16239,7 +16239,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16256,7 +16256,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16273,7 +16273,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16283,14 +16283,14 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16307,7 +16307,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16324,7 +16324,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16341,7 +16341,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16351,14 +16351,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16392,7 +16392,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16402,14 +16402,14 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16419,14 +16419,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16436,14 +16436,14 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16453,14 +16453,14 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16477,7 +16477,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16487,14 +16487,14 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16504,14 +16504,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16528,7 +16528,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16538,14 +16538,14 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16555,14 +16555,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16579,7 +16579,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16589,14 +16589,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16606,14 +16606,14 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16630,7 +16630,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16640,14 +16640,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -16681,7 +16681,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -16698,7 +16698,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -16708,14 +16708,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -16725,14 +16725,14 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -16742,14 +16742,14 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -16759,14 +16759,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -16776,14 +16776,14 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -16800,7 +16800,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -16817,7 +16817,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -16827,14 +16827,14 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -16844,14 +16844,14 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -16868,7 +16868,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -16902,7 +16902,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -16912,14 +16912,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -16929,14 +16929,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -16953,7 +16953,7 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -16963,14 +16963,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -16987,7 +16987,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -16997,14 +16997,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17014,14 +17014,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17038,7 +17038,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17055,7 +17055,7 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17065,14 +17065,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17089,7 +17089,7 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17106,7 +17106,7 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17116,14 +17116,14 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17140,7 +17140,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17150,14 +17150,14 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17167,14 +17167,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17184,14 +17184,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17201,14 +17201,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17225,7 +17225,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17242,7 +17242,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17259,7 +17259,7 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -17276,7 +17276,7 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -17293,7 +17293,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17310,7 +17310,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17327,7 +17327,7 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17337,14 +17337,14 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17354,14 +17354,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17371,14 +17371,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17388,14 +17388,14 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -17412,7 +17412,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17429,7 +17429,7 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17439,14 +17439,14 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17456,14 +17456,14 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -17473,14 +17473,14 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17497,7 +17497,7 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -17531,7 +17531,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17541,14 +17541,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17558,14 +17558,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17575,14 +17575,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17592,14 +17592,14 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17609,14 +17609,14 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17633,7 +17633,7 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17643,14 +17643,14 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -17660,14 +17660,14 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -17684,7 +17684,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -17701,7 +17701,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -17718,7 +17718,7 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -17735,7 +17735,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -17752,7 +17752,7 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -17769,7 +17769,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -17786,7 +17786,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -17803,7 +17803,7 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -17813,14 +17813,14 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -17837,7 +17837,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -17847,14 +17847,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -17871,7 +17871,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -17881,14 +17881,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -17898,14 +17898,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -17922,7 +17922,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -17939,7 +17939,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -17949,14 +17949,14 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -17966,14 +17966,14 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -17990,7 +17990,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18007,7 +18007,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18017,14 +18017,14 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -18034,14 +18034,14 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18058,7 +18058,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18075,7 +18075,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18085,14 +18085,14 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18102,14 +18102,14 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18119,14 +18119,14 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -18136,14 +18136,14 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -18153,14 +18153,14 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -18177,7 +18177,7 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -18194,7 +18194,7 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -18204,14 +18204,14 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -18228,7 +18228,7 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -18238,14 +18238,14 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -18262,7 +18262,7 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -18272,14 +18272,14 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -18296,7 +18296,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -18313,7 +18313,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -18323,14 +18323,14 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -18347,7 +18347,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -18364,7 +18364,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -18374,14 +18374,14 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -18398,7 +18398,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -18408,14 +18408,14 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -18425,14 +18425,14 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -18442,14 +18442,14 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -18466,7 +18466,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
@@ -18476,14 +18476,14 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -18500,7 +18500,7 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -18517,7 +18517,7 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -18527,14 +18527,14 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
@@ -18551,7 +18551,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
@@ -18561,14 +18561,14 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
@@ -18585,7 +18585,7 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -18602,7 +18602,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -18612,14 +18612,14 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -18636,7 +18636,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -18653,7 +18653,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -18670,7 +18670,7 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
@@ -18687,7 +18687,7 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
@@ -18704,7 +18704,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
@@ -18721,7 +18721,7 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18755,7 +18755,7 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -18765,14 +18765,14 @@
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -18782,14 +18782,14 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -18816,14 +18816,14 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -18833,14 +18833,14 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -18857,7 +18857,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -18874,7 +18874,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
@@ -18891,7 +18891,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -18908,7 +18908,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
@@ -18925,7 +18925,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -18935,14 +18935,14 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
@@ -18959,7 +18959,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -18969,14 +18969,14 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -18993,7 +18993,7 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -19003,14 +19003,14 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -19020,14 +19020,14 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
@@ -19044,7 +19044,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -19061,7 +19061,7 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -19078,7 +19078,7 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -19095,7 +19095,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -19112,7 +19112,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -19129,7 +19129,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -19146,7 +19146,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -19163,7 +19163,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -19173,14 +19173,14 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -19190,14 +19190,14 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -19207,14 +19207,14 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -19224,14 +19224,14 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -19248,7 +19248,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -19265,7 +19265,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -19282,7 +19282,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -19292,14 +19292,14 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -19309,14 +19309,14 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -19333,7 +19333,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -19343,14 +19343,14 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -19360,14 +19360,14 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -19384,7 +19384,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -19401,7 +19401,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -19418,7 +19418,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -19428,14 +19428,14 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -19452,7 +19452,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -19469,7 +19469,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -19486,7 +19486,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -19503,7 +19503,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -19537,7 +19537,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -19554,7 +19554,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -19571,7 +19571,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -19581,14 +19581,14 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -19598,14 +19598,14 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -19615,14 +19615,14 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -19632,14 +19632,14 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -19649,14 +19649,14 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -19673,7 +19673,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -19690,7 +19690,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -19700,14 +19700,14 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -19724,7 +19724,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -19734,7 +19734,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -19758,7 +19758,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -19775,7 +19775,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -19785,14 +19785,14 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -19802,14 +19802,14 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -19826,7 +19826,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -19843,7 +19843,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -19853,14 +19853,14 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -19870,14 +19870,14 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -19887,14 +19887,14 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -19904,14 +19904,14 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -19928,7 +19928,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -19938,14 +19938,14 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -19972,14 +19972,14 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -19996,7 +19996,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -20013,7 +20013,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -20047,7 +20047,7 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B675" t="inlineStr">
@@ -20057,14 +20057,14 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -20081,7 +20081,7 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
@@ -20098,7 +20098,7 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B678" t="inlineStr">
@@ -20108,14 +20108,14 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B679" t="inlineStr">
@@ -20125,7 +20125,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -20153,486 +20153,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CLABO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CLASS EDITORI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CY4Gate S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ECOSUNTEK S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ERG S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Energy Time S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Ferretti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>GVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Itway S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MARR S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Magis S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REPLY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>VNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>